--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.00863701674025</v>
+        <v>3.088903515220291</v>
       </c>
       <c r="D2" t="n">
-        <v>19.99844653612145</v>
+        <v>3.249747562119736</v>
       </c>
       <c r="E2" t="n">
-        <v>7.797642579333684</v>
+        <v>1.267116919141724</v>
       </c>
       <c r="F2" t="n">
-        <v>5.805790077626999</v>
+        <v>0.9434408876143874</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.98141342431799</v>
+        <v>2.759479681451673</v>
       </c>
       <c r="D3" t="n">
-        <v>10.54943113543649</v>
+        <v>1.71428255950843</v>
       </c>
       <c r="E3" t="n">
-        <v>7.797642579333684</v>
+        <v>1.267116919141724</v>
       </c>
       <c r="F3" t="n">
-        <v>5.805790077626999</v>
+        <v>0.9434408876143874</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.31326558623231</v>
+        <v>4.43840565776275</v>
       </c>
       <c r="D4" t="n">
-        <v>15.85117610253699</v>
+        <v>2.57581611666226</v>
       </c>
       <c r="E4" t="n">
-        <v>7.797642579333684</v>
+        <v>1.267116919141724</v>
       </c>
       <c r="F4" t="n">
-        <v>5.805790077626999</v>
+        <v>0.9434408876143874</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.82493973311449</v>
+        <v>5.009052706631104</v>
       </c>
       <c r="D5" t="n">
-        <v>20.12174061512542</v>
+        <v>3.269782849957881</v>
       </c>
       <c r="E5" t="n">
-        <v>7.797642579333684</v>
+        <v>1.267116919141724</v>
       </c>
       <c r="F5" t="n">
-        <v>5.805790077626999</v>
+        <v>0.9434408876143874</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.59742389066825</v>
+        <v>2.859581382233591</v>
       </c>
       <c r="D6" t="n">
-        <v>16.91591428992364</v>
+        <v>2.748836072112592</v>
       </c>
       <c r="E6" t="n">
-        <v>7.797642579333684</v>
+        <v>1.267116919141724</v>
       </c>
       <c r="F6" t="n">
-        <v>5.805790077626999</v>
+        <v>0.9434408876143874</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>5.063963717182259</v>
+        <v>0.822894104042117</v>
       </c>
       <c r="D7" t="n">
-        <v>4.312523866839928</v>
+        <v>0.7007851283614884</v>
       </c>
       <c r="E7" t="n">
-        <v>7.797642579333684</v>
+        <v>1.267116919141724</v>
       </c>
       <c r="F7" t="n">
-        <v>5.805790077626999</v>
+        <v>0.9434408876143874</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.939945011850323</v>
+        <v>1.452741064425678</v>
       </c>
       <c r="D8" t="n">
-        <v>9.695008395995202</v>
+        <v>1.575438864349221</v>
       </c>
       <c r="E8" t="n">
-        <v>7.797642579333684</v>
+        <v>1.267116919141724</v>
       </c>
       <c r="F8" t="n">
-        <v>5.805790077626999</v>
+        <v>0.9434408876143874</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>15.25932713955063</v>
+        <v>2.479640660176977</v>
       </c>
       <c r="D9" t="n">
-        <v>19.46837326867336</v>
+        <v>3.163610656159421</v>
       </c>
       <c r="E9" t="n">
-        <v>7.797642579333684</v>
+        <v>1.267116919141724</v>
       </c>
       <c r="F9" t="n">
-        <v>5.805790077626999</v>
+        <v>0.9434408876143874</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>15.87033579467543</v>
+        <v>2.578929566634757</v>
       </c>
       <c r="D10" t="n">
-        <v>15.45078214329315</v>
+        <v>2.510752098285137</v>
       </c>
       <c r="E10" t="n">
-        <v>7.797642579333684</v>
+        <v>1.267116919141724</v>
       </c>
       <c r="F10" t="n">
-        <v>5.805790077626999</v>
+        <v>0.9434408876143874</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>7.786196988603813</v>
+        <v>1.26525701064812</v>
       </c>
       <c r="D11" t="n">
-        <v>4.628293159590246</v>
+        <v>0.752097638433415</v>
       </c>
       <c r="E11" t="n">
-        <v>7.797642579333684</v>
+        <v>1.267116919141724</v>
       </c>
       <c r="F11" t="n">
-        <v>5.805790077626999</v>
+        <v>0.9434408876143874</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>7.492191201313181</v>
+        <v>1.217481070213392</v>
       </c>
       <c r="D12" t="n">
-        <v>6.888016496859789</v>
+        <v>1.119302680739716</v>
       </c>
       <c r="E12" t="n">
-        <v>7.797642579333684</v>
+        <v>1.267116919141724</v>
       </c>
       <c r="F12" t="n">
-        <v>5.805790077626999</v>
+        <v>0.9434408876143874</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
